--- a/Documentation Planning/pricing.xlsx
+++ b/Documentation Planning/pricing.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
-  <workbookPr/>
+  <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BAGUS BATRA\BB Photography\Documentation Planning\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BAGUS BATRA\BB-Photography\Documentation Planning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{750DD784-0161-4C45-BE83-AC74EC47CECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BCAA5CF-2EB8-415C-8F2D-972FD141243C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="16305" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MENU" sheetId="1" r:id="rId1"/>
@@ -21,8 +21,14 @@
     <sheet name="PREWEDDING" sheetId="6" r:id="rId6"/>
     <sheet name="WEDDING" sheetId="7" r:id="rId7"/>
     <sheet name="ENGAGEMENT" sheetId="8" r:id="rId8"/>
+    <sheet name="EVENT" sheetId="9" r:id="rId9"/>
+    <sheet name="TRAVEL" sheetId="10" r:id="rId10"/>
+    <sheet name="SIMULATION" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="5" r:id="rId12"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -46,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="118">
   <si>
     <t>Graduation Mini</t>
   </si>
@@ -313,21 +319,117 @@
     <t>Include Wedding Standard Package</t>
   </si>
   <si>
-    <t>next</t>
-  </si>
-  <si>
-    <t>Event
-Street 
-Architecture
-Travel
-Night</t>
+    <t>Engagement Mini</t>
+  </si>
+  <si>
+    <t>Event Standard</t>
+  </si>
+  <si>
+    <t>Event Pro</t>
+  </si>
+  <si>
+    <t>Event Corporate</t>
+  </si>
+  <si>
+    <t>12-15 Jam</t>
+  </si>
+  <si>
+    <t>2D1N</t>
+  </si>
+  <si>
+    <t>3D2N</t>
+  </si>
+  <si>
+    <t>Travel Standard</t>
+  </si>
+  <si>
+    <t>Travel Pro</t>
+  </si>
+  <si>
+    <t>Travel Complete</t>
+  </si>
+  <si>
+    <t>4D3N</t>
+  </si>
+  <si>
+    <t>School Discount</t>
+  </si>
+  <si>
+    <t>PACKAGE</t>
+  </si>
+  <si>
+    <t>Graduation</t>
+  </si>
+  <si>
+    <t>Stage 1</t>
+  </si>
+  <si>
+    <t>Stage 2</t>
+  </si>
+  <si>
+    <t>Stage 3</t>
+  </si>
+  <si>
+    <t>Stage 4</t>
+  </si>
+  <si>
+    <t>Client</t>
+  </si>
+  <si>
+    <t>Couple</t>
+  </si>
+  <si>
+    <t>Personal</t>
+  </si>
+  <si>
+    <t>Beauty</t>
+  </si>
+  <si>
+    <t>Prewedding</t>
+  </si>
+  <si>
+    <t>Wedding</t>
+  </si>
+  <si>
+    <t>Engagement</t>
+  </si>
+  <si>
+    <t>Event</t>
+  </si>
+  <si>
+    <t>Travel</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Sum of Stage 2</t>
+  </si>
+  <si>
+    <t>Sum of Stage 1</t>
+  </si>
+  <si>
+    <t>Sum of Stage 3</t>
+  </si>
+  <si>
+    <t>Sum of Stage 4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -352,6 +454,21 @@
     </font>
     <font>
       <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -390,10 +507,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -416,9 +534,6 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -434,8 +549,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -449,6 +582,3196 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[pricing.xlsx]SIMULATION!PivotTable1</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="9"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="10"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="11"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="12"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="13"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="14"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="15"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="16"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="17"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="18"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="19"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="20"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="21"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="22"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="23"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="24"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="25"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="26"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="27"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="28"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="29"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="30"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>SIMULATION!$C$14</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sum of Stage 1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>SIMULATION!$B$15:$B$24</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>Beauty</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Couple</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Engagement</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Event</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Graduation</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Personal</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Prewedding</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Travel</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Wedding</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>SIMULATION!$C$15:$C$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>700000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>940000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2200000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2080000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>860000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>900000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1940000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3360000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5200000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000A-7365-4A50-AF58-9FD72397EE1B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>SIMULATION!$D$14</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sum of Stage 2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>SIMULATION!$B$15:$B$24</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>Beauty</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Couple</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Engagement</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Event</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Graduation</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Personal</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Prewedding</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Travel</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Wedding</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>SIMULATION!$D$15:$D$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>1900000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1300000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3680000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3680000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1300000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1900000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3800000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6160000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9600000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000B-7365-4A50-AF58-9FD72397EE1B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>SIMULATION!$E$14</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sum of Stage 3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>SIMULATION!$B$15:$B$24</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>Beauty</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Couple</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Engagement</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Event</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Graduation</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Personal</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Prewedding</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Travel</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Wedding</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>SIMULATION!$E$15:$E$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2460000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6400000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6400000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2300000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3660000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7200000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>11200000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>15200000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000001C-7365-4A50-AF58-9FD72397EE1B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>SIMULATION!$F$14</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sum of Stage 4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>SIMULATION!$B$15:$B$24</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>Beauty</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Couple</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Engagement</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Event</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Graduation</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Personal</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Prewedding</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Travel</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Wedding</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>SIMULATION!$F$15:$F$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>19200000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19200000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3900000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>15200000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>21600000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>32800000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000001D-7365-4A50-AF58-9FD72397EE1B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1557188847"/>
+        <c:axId val="1557184527"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1557188847"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1557184527"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1557184527"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1557188847"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>142874</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>152401</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2140305-7D28-8305-0BA7-93EBE496A504}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="bagus batra" refreshedDate="46321.410347106481" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="9" xr:uid="{86571E55-2C53-4477-99D2-9F46A2F914CF}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="B2:G11" sheet="SIMULATION"/>
+  </cacheSource>
+  <cacheFields count="6">
+    <cacheField name="PACKAGE" numFmtId="0">
+      <sharedItems count="9">
+        <s v="Graduation"/>
+        <s v="Couple"/>
+        <s v="Personal"/>
+        <s v="Beauty"/>
+        <s v="Prewedding"/>
+        <s v="Wedding"/>
+        <s v="Engagement"/>
+        <s v="Event"/>
+        <s v="Travel"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Client" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="4" maxValue="4"/>
+    </cacheField>
+    <cacheField name="Stage 1" numFmtId="165">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="700000" maxValue="5200000" count="9">
+        <n v="860000"/>
+        <n v="940000"/>
+        <n v="900000"/>
+        <n v="700000"/>
+        <n v="1940000"/>
+        <n v="5200000"/>
+        <n v="2200000"/>
+        <n v="2080000"/>
+        <n v="3360000"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Stage 2" numFmtId="165">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1300000" maxValue="9600000" count="6">
+        <n v="1300000"/>
+        <n v="1900000"/>
+        <n v="3800000"/>
+        <n v="9600000"/>
+        <n v="3680000"/>
+        <n v="6160000"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Stage 3" numFmtId="165">
+      <sharedItems containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="2300000" maxValue="15200000"/>
+    </cacheField>
+    <cacheField name="Stage 4" numFmtId="165">
+      <sharedItems containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="3900000" maxValue="32800000"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="9">
+  <r>
+    <x v="0"/>
+    <n v="4"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="2300000"/>
+    <n v="3900000"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="4"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="2460000"/>
+    <s v="-"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="4"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="3660000"/>
+    <s v="-"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="4"/>
+    <x v="3"/>
+    <x v="1"/>
+    <s v="-"/>
+    <s v="-"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="4"/>
+    <x v="4"/>
+    <x v="2"/>
+    <n v="7200000"/>
+    <n v="15200000"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="4"/>
+    <x v="5"/>
+    <x v="3"/>
+    <n v="15200000"/>
+    <n v="32800000"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="4"/>
+    <x v="6"/>
+    <x v="4"/>
+    <n v="6400000"/>
+    <n v="19200000"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <n v="4"/>
+    <x v="7"/>
+    <x v="4"/>
+    <n v="6400000"/>
+    <n v="19200000"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <n v="4"/>
+    <x v="8"/>
+    <x v="5"/>
+    <n v="11200000"/>
+    <n v="21600000"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{76FA9080-9907-4BEB-ACB7-E85178F5C4E7}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="B14:F24" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="6">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="10">
+        <item x="3"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="165" showAll="0">
+      <items count="10">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item x="8"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="165" showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="10">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+    <i i="3">
+      <x v="3"/>
+    </i>
+  </colItems>
+  <dataFields count="4">
+    <dataField name="Sum of Stage 1" fld="2" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Stage 2" fld="3" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Stage 3" fld="4" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Stage 4" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="22">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="7" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="18" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="19" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="20" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="21" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="22" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="23" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="24" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="25" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="26" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="27" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="28" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="29" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="30" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -721,6 +4044,1035 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1071EBF4-91EE-4334-B20E-AE85B91A2517}">
+  <dimension ref="B1:G34"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="1"/>
+    <col min="2" max="2" width="36" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="1"/>
+    <col min="4" max="4" width="36" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="1"/>
+    <col min="6" max="6" width="18" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.85546875" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:7" ht="30" customHeight="1"/>
+    <row r="2" spans="2:7" ht="25.5" customHeight="1">
+      <c r="B2" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="13"/>
+    </row>
+    <row r="3" spans="2:7" ht="25.5" customHeight="1">
+      <c r="B3" s="3">
+        <v>840000</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1540000</v>
+      </c>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+    </row>
+    <row r="4" spans="2:7" ht="6" customHeight="1">
+      <c r="B4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+    </row>
+    <row r="5" spans="2:7">
+      <c r="B5" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="G5" s="6">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7">
+      <c r="B6" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="6">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7">
+      <c r="B7" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G7" s="6">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7">
+      <c r="B8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" s="6">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7">
+      <c r="D9" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7">
+      <c r="D10" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="10"/>
+      <c r="G10" s="11"/>
+    </row>
+    <row r="12" spans="2:7">
+      <c r="D12" s="10"/>
+    </row>
+    <row r="14" spans="2:7" ht="26.25" customHeight="1">
+      <c r="B14" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="13"/>
+    </row>
+    <row r="15" spans="2:7" ht="25.5" customHeight="1">
+      <c r="B15" s="3">
+        <v>2800000</v>
+      </c>
+      <c r="D15" s="3">
+        <v>5400000</v>
+      </c>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+    </row>
+    <row r="16" spans="2:7" ht="6.75" customHeight="1">
+      <c r="B16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+    </row>
+    <row r="17" spans="2:7">
+      <c r="B17" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" s="6">
+        <v>-50000</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7">
+      <c r="B18" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18" s="4" t="str">
+        <f>"-50000"&amp;" &amp; "&amp;"-25000"</f>
+        <v>-50000 &amp; -25000</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7">
+      <c r="B19" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19" s="7" t="str">
+        <f>"-50%"&amp;" All Type"</f>
+        <v>-50% All Type</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7">
+      <c r="B20" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G20" s="7" t="str">
+        <f>"-30%"&amp;" All Type"</f>
+        <v>-30% All Type</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7">
+      <c r="B21" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7">
+      <c r="B22" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7">
+      <c r="B23" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7">
+      <c r="D24" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" ht="15.75" customHeight="1"/>
+    <row r="26" spans="2:7" ht="15.75" customHeight="1"/>
+    <row r="34" spans="2:2">
+      <c r="B34" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="F2:G3"/>
+    <mergeCell ref="F14:G15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ED714A2-7F80-46E3-BC42-5E655D5C93B7}">
+  <dimension ref="B2:U42"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="1"/>
+    <col min="2" max="2" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="19" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="19" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:21">
+      <c r="B2" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="2:21">
+      <c r="B3" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C3" s="4">
+        <v>4</v>
+      </c>
+      <c r="D3" s="16">
+        <f>C3*GRADUATION!B3</f>
+        <v>860000</v>
+      </c>
+      <c r="E3" s="16">
+        <f>C3*GRADUATION!D3</f>
+        <v>1300000</v>
+      </c>
+      <c r="F3" s="16">
+        <f>C3*GRADUATION!B14</f>
+        <v>2300000</v>
+      </c>
+      <c r="G3" s="16">
+        <f>4*GRADUATION!D14</f>
+        <v>3900000</v>
+      </c>
+    </row>
+    <row r="4" spans="2:21">
+      <c r="B4" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" s="4">
+        <f>$C$3</f>
+        <v>4</v>
+      </c>
+      <c r="D4" s="16">
+        <f>C4*COUPLE!B3</f>
+        <v>940000</v>
+      </c>
+      <c r="E4" s="16">
+        <f>C4*COUPLE!D3</f>
+        <v>1300000</v>
+      </c>
+      <c r="F4" s="16">
+        <f>C4*COUPLE!B14</f>
+        <v>2460000</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" spans="2:21">
+      <c r="B5" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" s="4">
+        <f t="shared" ref="C5:C11" si="0">$C$3</f>
+        <v>4</v>
+      </c>
+      <c r="D5" s="16">
+        <f>C5*PERSONAL!B3</f>
+        <v>900000</v>
+      </c>
+      <c r="E5" s="16">
+        <f>C5*PERSONAL!D3</f>
+        <v>1900000</v>
+      </c>
+      <c r="F5" s="16">
+        <f>C5*PERSONAL!B14</f>
+        <v>3660000</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="2:21">
+      <c r="B6" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" s="4">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="D6" s="16">
+        <f>C6*BEAUTY!B3</f>
+        <v>700000</v>
+      </c>
+      <c r="E6" s="16">
+        <f>BEAUTY!D3*C6</f>
+        <v>1900000</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" spans="2:21">
+      <c r="B7" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" s="4">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="D7" s="16">
+        <f>C7*PREWEDDING!B3</f>
+        <v>1940000</v>
+      </c>
+      <c r="E7" s="16">
+        <f>C7*PREWEDDING!D3</f>
+        <v>3800000</v>
+      </c>
+      <c r="F7" s="16">
+        <f>C7*PREWEDDING!B15</f>
+        <v>7200000</v>
+      </c>
+      <c r="G7" s="16">
+        <f>C7*PREWEDDING!D15</f>
+        <v>15200000</v>
+      </c>
+    </row>
+    <row r="8" spans="2:21">
+      <c r="B8" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C8" s="4">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="D8" s="16">
+        <f>C8*WEDDING!B3</f>
+        <v>5200000</v>
+      </c>
+      <c r="E8" s="16">
+        <f>C8*WEDDING!D3</f>
+        <v>9600000</v>
+      </c>
+      <c r="F8" s="16">
+        <f>C8*WEDDING!B15</f>
+        <v>15200000</v>
+      </c>
+      <c r="G8" s="16">
+        <f>C8*WEDDING!D15</f>
+        <v>32800000</v>
+      </c>
+    </row>
+    <row r="9" spans="2:21">
+      <c r="B9" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9" s="4">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="D9" s="16">
+        <f>C9*ENGAGEMENT!B3</f>
+        <v>2200000</v>
+      </c>
+      <c r="E9" s="16">
+        <f>C9*ENGAGEMENT!D3</f>
+        <v>3680000</v>
+      </c>
+      <c r="F9" s="16">
+        <f>C9*ENGAGEMENT!B15</f>
+        <v>6400000</v>
+      </c>
+      <c r="G9" s="16">
+        <f>C9*ENGAGEMENT!D15</f>
+        <v>19200000</v>
+      </c>
+    </row>
+    <row r="10" spans="2:21">
+      <c r="B10" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C10" s="4">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="D10" s="16">
+        <f>C10*EVENT!B3</f>
+        <v>2080000</v>
+      </c>
+      <c r="E10" s="16">
+        <f>C10*EVENT!D3</f>
+        <v>3680000</v>
+      </c>
+      <c r="F10" s="16">
+        <f>C10*EVENT!B15</f>
+        <v>6400000</v>
+      </c>
+      <c r="G10" s="16">
+        <f>C10*EVENT!D15</f>
+        <v>19200000</v>
+      </c>
+    </row>
+    <row r="11" spans="2:21">
+      <c r="B11" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C11" s="4">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="D11" s="16">
+        <f>C11*TRAVEL!B3</f>
+        <v>3360000</v>
+      </c>
+      <c r="E11" s="16">
+        <f>C11*TRAVEL!D3</f>
+        <v>6160000</v>
+      </c>
+      <c r="F11" s="16">
+        <f>C11*TRAVEL!B15</f>
+        <v>11200000</v>
+      </c>
+      <c r="G11" s="16">
+        <f>C11*TRAVEL!D15</f>
+        <v>21600000</v>
+      </c>
+    </row>
+    <row r="14" spans="2:21">
+      <c r="B14" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="C14" t="s">
+        <v>115</v>
+      </c>
+      <c r="D14" t="s">
+        <v>114</v>
+      </c>
+      <c r="E14" t="s">
+        <v>116</v>
+      </c>
+      <c r="F14" t="s">
+        <v>117</v>
+      </c>
+      <c r="G14"/>
+      <c r="H14"/>
+      <c r="I14"/>
+      <c r="J14"/>
+      <c r="K14"/>
+      <c r="L14"/>
+      <c r="M14"/>
+      <c r="N14"/>
+      <c r="O14"/>
+      <c r="P14"/>
+      <c r="Q14"/>
+      <c r="R14"/>
+      <c r="S14"/>
+      <c r="T14"/>
+      <c r="U14"/>
+    </row>
+    <row r="15" spans="2:21">
+      <c r="B15" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="C15" s="19">
+        <v>700000</v>
+      </c>
+      <c r="D15" s="19">
+        <v>1900000</v>
+      </c>
+      <c r="E15" s="19">
+        <v>0</v>
+      </c>
+      <c r="F15" s="19">
+        <v>0</v>
+      </c>
+      <c r="G15"/>
+      <c r="H15"/>
+      <c r="I15"/>
+      <c r="J15"/>
+      <c r="K15"/>
+      <c r="L15"/>
+      <c r="M15"/>
+      <c r="N15"/>
+      <c r="O15"/>
+      <c r="P15"/>
+      <c r="Q15"/>
+      <c r="R15"/>
+      <c r="S15"/>
+      <c r="T15"/>
+      <c r="U15"/>
+    </row>
+    <row r="16" spans="2:21">
+      <c r="B16" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C16" s="19">
+        <v>940000</v>
+      </c>
+      <c r="D16" s="19">
+        <v>1300000</v>
+      </c>
+      <c r="E16" s="19">
+        <v>2460000</v>
+      </c>
+      <c r="F16" s="19">
+        <v>0</v>
+      </c>
+      <c r="G16"/>
+      <c r="H16"/>
+      <c r="I16"/>
+      <c r="J16"/>
+      <c r="K16"/>
+      <c r="L16"/>
+      <c r="M16"/>
+      <c r="N16"/>
+      <c r="O16"/>
+      <c r="P16"/>
+      <c r="Q16"/>
+      <c r="R16"/>
+      <c r="S16"/>
+      <c r="T16"/>
+      <c r="U16"/>
+    </row>
+    <row r="17" spans="2:21">
+      <c r="B17" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" s="19">
+        <v>2200000</v>
+      </c>
+      <c r="D17" s="19">
+        <v>3680000</v>
+      </c>
+      <c r="E17" s="19">
+        <v>6400000</v>
+      </c>
+      <c r="F17" s="19">
+        <v>19200000</v>
+      </c>
+      <c r="G17"/>
+      <c r="H17"/>
+      <c r="I17"/>
+      <c r="J17"/>
+      <c r="K17"/>
+      <c r="L17"/>
+      <c r="M17"/>
+      <c r="N17"/>
+      <c r="O17"/>
+      <c r="P17"/>
+      <c r="Q17"/>
+      <c r="R17"/>
+      <c r="S17"/>
+      <c r="T17"/>
+      <c r="U17"/>
+    </row>
+    <row r="18" spans="2:21">
+      <c r="B18" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="C18" s="19">
+        <v>2080000</v>
+      </c>
+      <c r="D18" s="19">
+        <v>3680000</v>
+      </c>
+      <c r="E18" s="19">
+        <v>6400000</v>
+      </c>
+      <c r="F18" s="19">
+        <v>19200000</v>
+      </c>
+      <c r="G18"/>
+      <c r="H18"/>
+      <c r="I18"/>
+      <c r="J18"/>
+      <c r="K18"/>
+      <c r="L18"/>
+      <c r="M18"/>
+      <c r="N18"/>
+      <c r="O18"/>
+      <c r="P18"/>
+      <c r="Q18"/>
+      <c r="R18"/>
+      <c r="S18"/>
+      <c r="T18"/>
+      <c r="U18"/>
+    </row>
+    <row r="19" spans="2:21">
+      <c r="B19" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C19" s="19">
+        <v>860000</v>
+      </c>
+      <c r="D19" s="19">
+        <v>1300000</v>
+      </c>
+      <c r="E19" s="19">
+        <v>2300000</v>
+      </c>
+      <c r="F19" s="19">
+        <v>3900000</v>
+      </c>
+      <c r="G19"/>
+      <c r="H19"/>
+      <c r="I19"/>
+      <c r="J19"/>
+      <c r="K19"/>
+      <c r="L19"/>
+      <c r="M19"/>
+      <c r="N19"/>
+      <c r="O19"/>
+      <c r="P19"/>
+      <c r="Q19"/>
+      <c r="R19"/>
+      <c r="S19"/>
+      <c r="T19"/>
+      <c r="U19"/>
+    </row>
+    <row r="20" spans="2:21">
+      <c r="B20" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="C20" s="19">
+        <v>900000</v>
+      </c>
+      <c r="D20" s="19">
+        <v>1900000</v>
+      </c>
+      <c r="E20" s="19">
+        <v>3660000</v>
+      </c>
+      <c r="F20" s="19">
+        <v>0</v>
+      </c>
+      <c r="G20"/>
+      <c r="H20"/>
+      <c r="I20"/>
+      <c r="J20"/>
+      <c r="K20"/>
+      <c r="L20"/>
+      <c r="M20"/>
+      <c r="N20"/>
+      <c r="O20"/>
+      <c r="P20"/>
+      <c r="Q20"/>
+      <c r="R20"/>
+      <c r="S20"/>
+      <c r="T20"/>
+      <c r="U20"/>
+    </row>
+    <row r="21" spans="2:21">
+      <c r="B21" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="C21" s="19">
+        <v>1940000</v>
+      </c>
+      <c r="D21" s="19">
+        <v>3800000</v>
+      </c>
+      <c r="E21" s="19">
+        <v>7200000</v>
+      </c>
+      <c r="F21" s="19">
+        <v>15200000</v>
+      </c>
+      <c r="G21"/>
+      <c r="H21"/>
+      <c r="I21"/>
+      <c r="J21"/>
+      <c r="K21"/>
+      <c r="L21"/>
+      <c r="M21"/>
+      <c r="N21"/>
+      <c r="O21"/>
+      <c r="P21"/>
+      <c r="Q21"/>
+      <c r="R21"/>
+      <c r="S21"/>
+      <c r="T21"/>
+      <c r="U21"/>
+    </row>
+    <row r="22" spans="2:21">
+      <c r="B22" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="C22" s="19">
+        <v>3360000</v>
+      </c>
+      <c r="D22" s="19">
+        <v>6160000</v>
+      </c>
+      <c r="E22" s="19">
+        <v>11200000</v>
+      </c>
+      <c r="F22" s="19">
+        <v>21600000</v>
+      </c>
+      <c r="G22"/>
+      <c r="H22"/>
+      <c r="I22"/>
+      <c r="J22"/>
+      <c r="K22"/>
+      <c r="L22"/>
+      <c r="M22"/>
+      <c r="N22"/>
+      <c r="O22"/>
+      <c r="P22"/>
+      <c r="Q22"/>
+      <c r="R22"/>
+      <c r="S22"/>
+      <c r="T22"/>
+      <c r="U22"/>
+    </row>
+    <row r="23" spans="2:21">
+      <c r="B23" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C23" s="19">
+        <v>5200000</v>
+      </c>
+      <c r="D23" s="19">
+        <v>9600000</v>
+      </c>
+      <c r="E23" s="19">
+        <v>15200000</v>
+      </c>
+      <c r="F23" s="19">
+        <v>32800000</v>
+      </c>
+      <c r="G23"/>
+      <c r="H23"/>
+      <c r="I23"/>
+      <c r="J23"/>
+      <c r="K23"/>
+      <c r="L23"/>
+      <c r="M23"/>
+      <c r="N23"/>
+      <c r="O23"/>
+      <c r="P23"/>
+      <c r="Q23"/>
+      <c r="R23"/>
+      <c r="S23"/>
+      <c r="T23"/>
+      <c r="U23"/>
+    </row>
+    <row r="24" spans="2:21">
+      <c r="B24" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="C24" s="19">
+        <v>18180000</v>
+      </c>
+      <c r="D24" s="19">
+        <v>33320000</v>
+      </c>
+      <c r="E24" s="19">
+        <v>54820000</v>
+      </c>
+      <c r="F24" s="19">
+        <v>111900000</v>
+      </c>
+      <c r="G24"/>
+      <c r="H24"/>
+      <c r="I24"/>
+      <c r="J24"/>
+      <c r="K24"/>
+      <c r="L24"/>
+      <c r="M24"/>
+      <c r="N24"/>
+      <c r="O24"/>
+      <c r="P24"/>
+      <c r="Q24"/>
+      <c r="R24"/>
+      <c r="S24"/>
+      <c r="T24"/>
+      <c r="U24"/>
+    </row>
+    <row r="25" spans="2:21">
+      <c r="B25"/>
+      <c r="C25"/>
+      <c r="D25"/>
+      <c r="E25"/>
+      <c r="F25"/>
+      <c r="G25"/>
+      <c r="H25"/>
+      <c r="I25"/>
+      <c r="J25"/>
+      <c r="K25"/>
+      <c r="L25"/>
+      <c r="M25"/>
+      <c r="N25"/>
+      <c r="O25"/>
+      <c r="P25"/>
+      <c r="Q25"/>
+      <c r="R25"/>
+      <c r="S25"/>
+      <c r="T25"/>
+      <c r="U25"/>
+    </row>
+    <row r="26" spans="2:21">
+      <c r="B26"/>
+      <c r="C26"/>
+      <c r="D26"/>
+      <c r="E26"/>
+      <c r="F26"/>
+      <c r="G26"/>
+      <c r="H26"/>
+      <c r="I26"/>
+      <c r="J26"/>
+      <c r="K26"/>
+      <c r="L26"/>
+      <c r="M26"/>
+      <c r="N26"/>
+      <c r="O26"/>
+      <c r="P26"/>
+      <c r="Q26"/>
+      <c r="R26"/>
+      <c r="S26"/>
+      <c r="T26"/>
+      <c r="U26"/>
+    </row>
+    <row r="27" spans="2:21">
+      <c r="B27"/>
+      <c r="C27"/>
+      <c r="D27"/>
+      <c r="E27"/>
+      <c r="F27"/>
+      <c r="G27"/>
+      <c r="H27"/>
+      <c r="I27"/>
+      <c r="J27"/>
+      <c r="K27"/>
+      <c r="L27"/>
+    </row>
+    <row r="28" spans="2:21">
+      <c r="B28"/>
+      <c r="C28"/>
+      <c r="D28"/>
+      <c r="E28"/>
+      <c r="F28"/>
+      <c r="G28"/>
+      <c r="H28"/>
+      <c r="I28"/>
+      <c r="J28"/>
+      <c r="K28"/>
+      <c r="L28"/>
+    </row>
+    <row r="29" spans="2:21">
+      <c r="B29"/>
+      <c r="C29"/>
+      <c r="D29"/>
+      <c r="E29"/>
+      <c r="F29"/>
+      <c r="G29"/>
+      <c r="H29"/>
+      <c r="I29"/>
+      <c r="J29"/>
+      <c r="K29"/>
+      <c r="L29"/>
+    </row>
+    <row r="30" spans="2:21">
+      <c r="B30"/>
+      <c r="C30"/>
+      <c r="D30"/>
+      <c r="E30"/>
+      <c r="F30"/>
+      <c r="G30"/>
+      <c r="H30"/>
+      <c r="I30"/>
+      <c r="J30"/>
+      <c r="K30"/>
+      <c r="L30"/>
+    </row>
+    <row r="31" spans="2:21">
+      <c r="B31"/>
+      <c r="C31"/>
+      <c r="D31"/>
+      <c r="E31"/>
+      <c r="F31"/>
+      <c r="G31"/>
+      <c r="H31"/>
+      <c r="I31"/>
+      <c r="J31"/>
+      <c r="K31"/>
+      <c r="L31"/>
+    </row>
+    <row r="32" spans="2:21">
+      <c r="B32"/>
+      <c r="C32"/>
+      <c r="D32"/>
+      <c r="E32"/>
+      <c r="F32"/>
+      <c r="G32"/>
+      <c r="H32"/>
+      <c r="I32"/>
+      <c r="J32"/>
+      <c r="K32"/>
+      <c r="L32"/>
+    </row>
+    <row r="33" spans="2:12">
+      <c r="B33"/>
+      <c r="C33"/>
+      <c r="D33"/>
+      <c r="E33"/>
+      <c r="F33"/>
+      <c r="G33"/>
+      <c r="H33"/>
+      <c r="I33"/>
+      <c r="J33"/>
+      <c r="K33"/>
+      <c r="L33"/>
+    </row>
+    <row r="34" spans="2:12">
+      <c r="B34"/>
+      <c r="C34"/>
+      <c r="D34"/>
+      <c r="E34"/>
+      <c r="F34"/>
+      <c r="G34"/>
+      <c r="H34"/>
+      <c r="I34"/>
+      <c r="J34"/>
+      <c r="K34"/>
+      <c r="L34"/>
+    </row>
+    <row r="35" spans="2:12">
+      <c r="B35"/>
+    </row>
+    <row r="36" spans="2:12">
+      <c r="B36"/>
+    </row>
+    <row r="37" spans="2:12">
+      <c r="B37"/>
+    </row>
+    <row r="38" spans="2:12">
+      <c r="B38"/>
+    </row>
+    <row r="39" spans="2:12">
+      <c r="B39"/>
+    </row>
+    <row r="40" spans="2:12">
+      <c r="B40"/>
+    </row>
+    <row r="41" spans="2:12">
+      <c r="B41"/>
+    </row>
+    <row r="42" spans="2:12">
+      <c r="B42"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BA0498E-CFF0-4389-A69A-34CB8E5E601C}">
   <dimension ref="B1:G25"/>
@@ -744,10 +5096,10 @@
       <c r="D2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="5"/>
+      <c r="G2" s="13"/>
     </row>
     <row r="3" spans="2:7" ht="25.5" customHeight="1">
       <c r="B3" s="3">
@@ -756,8 +5108,8 @@
       <c r="D3" s="3">
         <v>325000</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
     </row>
     <row r="4" spans="2:7" ht="6" customHeight="1">
       <c r="B4" s="4"/>
@@ -839,10 +5191,10 @@
       <c r="D13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="G13" s="5"/>
+      <c r="G13" s="13"/>
     </row>
     <row r="14" spans="2:7" ht="25.5" customHeight="1">
       <c r="B14" s="3">
@@ -851,8 +5203,8 @@
       <c r="D14" s="3">
         <v>975000</v>
       </c>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
     </row>
     <row r="15" spans="2:7" ht="6.75" customHeight="1">
       <c r="B15" s="4"/>
@@ -962,10 +5314,10 @@
       <c r="D2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="5"/>
+      <c r="G2" s="13"/>
     </row>
     <row r="3" spans="2:7" ht="25.5" customHeight="1">
       <c r="B3" s="3">
@@ -974,8 +5326,8 @@
       <c r="D3" s="3">
         <v>325000</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
     </row>
     <row r="4" spans="2:7" ht="6" customHeight="1">
       <c r="B4" s="4"/>
@@ -1054,23 +5406,23 @@
       <c r="B13" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="9"/>
-      <c r="F13" s="8" t="s">
+      <c r="D13" s="8"/>
+      <c r="F13" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="G13" s="5"/>
+      <c r="G13" s="13"/>
     </row>
     <row r="14" spans="2:7" ht="25.5" customHeight="1">
       <c r="B14" s="3">
         <v>615000</v>
       </c>
-      <c r="D14" s="10"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
+      <c r="D14" s="9"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
     </row>
     <row r="15" spans="2:7" ht="6.75" customHeight="1">
       <c r="B15" s="4"/>
-      <c r="D15" s="11"/>
+      <c r="D15" s="10"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
     </row>
@@ -1078,7 +5430,7 @@
       <c r="B16" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="11"/>
+      <c r="D16" s="10"/>
       <c r="F16" s="4" t="s">
         <v>20</v>
       </c>
@@ -1090,7 +5442,7 @@
       <c r="B17" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="11"/>
+      <c r="D17" s="10"/>
       <c r="F17" s="4" t="s">
         <v>21</v>
       </c>
@@ -1103,7 +5455,7 @@
       <c r="B18" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="11"/>
+      <c r="D18" s="10"/>
       <c r="F18" s="4" t="s">
         <v>22</v>
       </c>
@@ -1116,19 +5468,19 @@
       <c r="B19" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D19" s="11"/>
+      <c r="D19" s="10"/>
     </row>
     <row r="20" spans="2:7">
       <c r="B20" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="11"/>
+      <c r="D20" s="10"/>
     </row>
     <row r="21" spans="2:7">
       <c r="B21" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D21" s="11"/>
+      <c r="D21" s="10"/>
     </row>
     <row r="22" spans="2:7">
       <c r="B22" s="4" t="s">
@@ -1169,10 +5521,10 @@
       <c r="D2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="5"/>
+      <c r="G2" s="13"/>
     </row>
     <row r="3" spans="2:7" ht="25.5" customHeight="1">
       <c r="B3" s="3">
@@ -1181,8 +5533,8 @@
       <c r="D3" s="3">
         <v>475000</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
     </row>
     <row r="4" spans="2:7" ht="6" customHeight="1">
       <c r="B4" s="4"/>
@@ -1266,23 +5618,23 @@
       <c r="B13" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="9"/>
-      <c r="F13" s="8" t="s">
+      <c r="D13" s="8"/>
+      <c r="F13" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="G13" s="5"/>
+      <c r="G13" s="13"/>
     </row>
     <row r="14" spans="2:7" ht="25.5" customHeight="1">
       <c r="B14" s="3">
         <v>915000</v>
       </c>
-      <c r="D14" s="10"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
+      <c r="D14" s="9"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
     </row>
     <row r="15" spans="2:7" ht="6.75" customHeight="1">
       <c r="B15" s="4"/>
-      <c r="D15" s="11"/>
+      <c r="D15" s="10"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
     </row>
@@ -1290,7 +5642,7 @@
       <c r="B16" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="11"/>
+      <c r="D16" s="10"/>
       <c r="F16" s="4" t="s">
         <v>20</v>
       </c>
@@ -1302,7 +5654,7 @@
       <c r="B17" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="11"/>
+      <c r="D17" s="10"/>
       <c r="F17" s="4" t="s">
         <v>21</v>
       </c>
@@ -1315,7 +5667,7 @@
       <c r="B18" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="11"/>
+      <c r="D18" s="10"/>
       <c r="F18" s="4" t="s">
         <v>22</v>
       </c>
@@ -1328,19 +5680,19 @@
       <c r="B19" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D19" s="11"/>
+      <c r="D19" s="10"/>
     </row>
     <row r="20" spans="2:7">
       <c r="B20" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="11"/>
+      <c r="D20" s="10"/>
     </row>
     <row r="21" spans="2:7">
       <c r="B21" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="11"/>
+      <c r="D21" s="10"/>
     </row>
     <row r="22" spans="2:7">
       <c r="B22" s="4" t="s">
@@ -1381,10 +5733,10 @@
       <c r="D2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="5"/>
+      <c r="G2" s="13"/>
     </row>
     <row r="3" spans="2:7" ht="25.5" customHeight="1">
       <c r="B3" s="3">
@@ -1393,8 +5745,8 @@
       <c r="D3" s="3">
         <v>475000</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
     </row>
     <row r="4" spans="2:7" ht="6" customHeight="1">
       <c r="B4" s="4"/>
@@ -1480,28 +5832,28 @@
       </c>
     </row>
     <row r="13" spans="2:7" ht="26.25" customHeight="1">
-      <c r="B13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="F13" s="8" t="s">
+      <c r="B13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="F13" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="G13" s="5"/>
+      <c r="G13" s="13"/>
     </row>
     <row r="14" spans="2:7" ht="25.5" customHeight="1">
-      <c r="B14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
+      <c r="B14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
     </row>
     <row r="15" spans="2:7" ht="6.75" customHeight="1">
-      <c r="B15" s="11"/>
-      <c r="D15" s="11"/>
+      <c r="B15" s="10"/>
+      <c r="D15" s="10"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
     </row>
     <row r="16" spans="2:7">
-      <c r="B16" s="11"/>
-      <c r="D16" s="11"/>
+      <c r="B16" s="10"/>
+      <c r="D16" s="10"/>
       <c r="F16" s="4" t="s">
         <v>20</v>
       </c>
@@ -1510,8 +5862,8 @@
       </c>
     </row>
     <row r="17" spans="2:7">
-      <c r="B17" s="11"/>
-      <c r="D17" s="11"/>
+      <c r="B17" s="10"/>
+      <c r="D17" s="10"/>
       <c r="F17" s="4" t="s">
         <v>21</v>
       </c>
@@ -1521,8 +5873,8 @@
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="11"/>
-      <c r="D18" s="11"/>
+      <c r="B18" s="10"/>
+      <c r="D18" s="10"/>
       <c r="F18" s="4" t="s">
         <v>22</v>
       </c>
@@ -1532,19 +5884,19 @@
       </c>
     </row>
     <row r="19" spans="2:7">
-      <c r="B19" s="11"/>
-      <c r="D19" s="11"/>
+      <c r="B19" s="10"/>
+      <c r="D19" s="10"/>
     </row>
     <row r="20" spans="2:7">
-      <c r="B20" s="11"/>
-      <c r="D20" s="11"/>
+      <c r="B20" s="10"/>
+      <c r="D20" s="10"/>
     </row>
     <row r="21" spans="2:7">
-      <c r="B21" s="11"/>
-      <c r="D21" s="11"/>
+      <c r="B21" s="10"/>
+      <c r="D21" s="10"/>
     </row>
     <row r="22" spans="2:7">
-      <c r="B22" s="11"/>
+      <c r="B22" s="10"/>
     </row>
     <row r="25" spans="2:7" ht="26.25" customHeight="1"/>
   </sheetData>
@@ -1580,10 +5932,10 @@
       <c r="D2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="5"/>
+      <c r="G2" s="13"/>
     </row>
     <row r="3" spans="2:7" ht="25.5" customHeight="1">
       <c r="B3" s="3">
@@ -1592,8 +5944,8 @@
       <c r="D3" s="3">
         <v>950000</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
     </row>
     <row r="4" spans="2:7" ht="6" customHeight="1">
       <c r="B4" s="4"/>
@@ -1669,8 +6021,8 @@
       <c r="D10" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F10" s="11"/>
-      <c r="G10" s="12"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="11"/>
     </row>
     <row r="11" spans="2:7">
       <c r="D11" s="4" t="s">
@@ -1678,7 +6030,7 @@
       </c>
     </row>
     <row r="12" spans="2:7">
-      <c r="D12" s="11"/>
+      <c r="D12" s="10"/>
     </row>
     <row r="14" spans="2:7" ht="26.25" customHeight="1">
       <c r="B14" s="2" t="s">
@@ -1687,10 +6039,10 @@
       <c r="D14" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="G14" s="5"/>
+      <c r="G14" s="13"/>
     </row>
     <row r="15" spans="2:7" ht="25.5" customHeight="1">
       <c r="B15" s="3">
@@ -1699,8 +6051,8 @@
       <c r="D15" s="3">
         <v>3800000</v>
       </c>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
     </row>
     <row r="16" spans="2:7" ht="6.75" customHeight="1">
       <c r="B16" s="4"/>
@@ -1853,10 +6205,10 @@
       <c r="D2" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="5"/>
+      <c r="G2" s="13"/>
     </row>
     <row r="3" spans="2:7" ht="25.5" customHeight="1">
       <c r="B3" s="3">
@@ -1865,8 +6217,8 @@
       <c r="D3" s="3">
         <v>2400000</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
     </row>
     <row r="4" spans="2:7" ht="6" customHeight="1">
       <c r="B4" s="4"/>
@@ -1942,11 +6294,11 @@
       <c r="D10" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F10" s="11"/>
-      <c r="G10" s="12"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="11"/>
     </row>
     <row r="12" spans="2:7">
-      <c r="D12" s="11"/>
+      <c r="D12" s="10"/>
     </row>
     <row r="14" spans="2:7" ht="26.25" customHeight="1">
       <c r="B14" s="2" t="s">
@@ -1955,10 +6307,10 @@
       <c r="D14" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="G14" s="5"/>
+      <c r="G14" s="13"/>
     </row>
     <row r="15" spans="2:7" ht="25.5" customHeight="1">
       <c r="B15" s="3">
@@ -1967,8 +6319,8 @@
       <c r="D15" s="3">
         <v>8200000</v>
       </c>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
     </row>
     <row r="16" spans="2:7" ht="6.75" customHeight="1">
       <c r="B16" s="4"/>
@@ -2105,15 +6457,15 @@
     <row r="1" spans="2:7" ht="30" customHeight="1"/>
     <row r="2" spans="2:7" ht="25.5" customHeight="1">
       <c r="B2" s="2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="5"/>
+      <c r="G2" s="13"/>
     </row>
     <row r="3" spans="2:7" ht="25.5" customHeight="1">
       <c r="B3" s="3">
@@ -2122,8 +6474,8 @@
       <c r="D3" s="3">
         <v>920000</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
     </row>
     <row r="4" spans="2:7" ht="6" customHeight="1">
       <c r="B4" s="4"/>
@@ -2199,11 +6551,11 @@
       <c r="D10" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F10" s="11"/>
-      <c r="G10" s="12"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="11"/>
     </row>
     <row r="12" spans="2:7">
-      <c r="D12" s="11"/>
+      <c r="D12" s="10"/>
     </row>
     <row r="14" spans="2:7" ht="26.25" customHeight="1">
       <c r="B14" s="2" t="s">
@@ -2212,10 +6564,10 @@
       <c r="D14" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="G14" s="5"/>
+      <c r="G14" s="13"/>
     </row>
     <row r="15" spans="2:7" ht="25.5" customHeight="1">
       <c r="B15" s="3">
@@ -2224,8 +6576,8 @@
       <c r="D15" s="3">
         <v>4800000</v>
       </c>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
     </row>
     <row r="16" spans="2:7" ht="6.75" customHeight="1">
       <c r="B16" s="4"/>
@@ -2329,15 +6681,247 @@
         <v>59</v>
       </c>
     </row>
-    <row r="33" spans="2:2">
-      <c r="B33" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2" ht="75">
-      <c r="B34" s="13" t="s">
+    <row r="34" spans="2:2">
+      <c r="B34" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="F2:G3"/>
+    <mergeCell ref="F14:G15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{124CE633-E2C2-45EB-9187-AAB4045A946D}">
+  <dimension ref="B1:G34"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="1"/>
+    <col min="2" max="2" width="36" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="1"/>
+    <col min="4" max="4" width="36" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="1"/>
+    <col min="6" max="6" width="18" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.85546875" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:7" ht="30" customHeight="1"/>
+    <row r="2" spans="2:7" ht="25.5" customHeight="1">
+      <c r="B2" s="5" t="s">
         <v>85</v>
       </c>
+      <c r="D2" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="13"/>
+    </row>
+    <row r="3" spans="2:7" ht="25.5" customHeight="1">
+      <c r="B3" s="3">
+        <v>520000</v>
+      </c>
+      <c r="D3" s="3">
+        <v>920000</v>
+      </c>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+    </row>
+    <row r="4" spans="2:7" ht="6" customHeight="1">
+      <c r="B4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+    </row>
+    <row r="5" spans="2:7">
+      <c r="B5" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="G5" s="6">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7">
+      <c r="B6" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="6">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7">
+      <c r="B7" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G7" s="6">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7">
+      <c r="B8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" s="6">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7">
+      <c r="D9" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7">
+      <c r="D10" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="10"/>
+      <c r="G10" s="11"/>
+    </row>
+    <row r="12" spans="2:7">
+      <c r="D12" s="10"/>
+    </row>
+    <row r="14" spans="2:7" ht="26.25" customHeight="1">
+      <c r="B14" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="13"/>
+    </row>
+    <row r="15" spans="2:7" ht="25.5" customHeight="1">
+      <c r="B15" s="3">
+        <v>1600000</v>
+      </c>
+      <c r="D15" s="3">
+        <v>4800000</v>
+      </c>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+    </row>
+    <row r="16" spans="2:7" ht="6.75" customHeight="1">
+      <c r="B16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+    </row>
+    <row r="17" spans="2:7">
+      <c r="B17" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" s="6">
+        <v>-50000</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7">
+      <c r="B18" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18" s="4" t="str">
+        <f>"-50000"&amp;" &amp; "&amp;"-25000"</f>
+        <v>-50000 &amp; -25000</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7">
+      <c r="B19" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19" s="7" t="str">
+        <f>"-50%"&amp;" All Type"</f>
+        <v>-50% All Type</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7">
+      <c r="B20" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7">
+      <c r="B21" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7">
+      <c r="B22" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7">
+      <c r="B23" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7">
+      <c r="D24" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" ht="15.75" customHeight="1"/>
+    <row r="26" spans="2:7" ht="15.75" customHeight="1"/>
+    <row r="34" spans="2:2">
+      <c r="B34" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Documentation Planning/pricing.xlsx
+++ b/Documentation Planning/pricing.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BAGUS BATRA\BB-Photography\Documentation Planning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BCAA5CF-2EB8-415C-8F2D-972FD141243C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF6EDCF2-2DAF-4278-B0A3-E46D32C7F6B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MENU" sheetId="1" r:id="rId1"/>
-    <sheet name="GRADUATION" sheetId="2" r:id="rId2"/>
-    <sheet name="COUPLE" sheetId="3" r:id="rId3"/>
-    <sheet name="PERSONAL" sheetId="4" r:id="rId4"/>
-    <sheet name="BEAUTY" sheetId="5" r:id="rId5"/>
+    <sheet name="PERSONAL" sheetId="4" r:id="rId2"/>
+    <sheet name="BEAUTY" sheetId="5" r:id="rId3"/>
+    <sheet name="GRADUATION" sheetId="2" r:id="rId4"/>
+    <sheet name="COUPLE" sheetId="3" r:id="rId5"/>
     <sheet name="PREWEDDING" sheetId="6" r:id="rId6"/>
     <sheet name="WEDDING" sheetId="7" r:id="rId7"/>
     <sheet name="ENGAGEMENT" sheetId="8" r:id="rId8"/>
@@ -27,7 +27,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId12"/>
+    <pivotCache cacheId="0" r:id="rId12"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -427,9 +427,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -549,16 +549,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -566,6 +560,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -3315,7 +3315,7 @@
     <cacheField name="Client" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="4" maxValue="4"/>
     </cacheField>
-    <cacheField name="Stage 1" numFmtId="165">
+    <cacheField name="Stage 1" numFmtId="164">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="700000" maxValue="5200000" count="9">
         <n v="860000"/>
         <n v="940000"/>
@@ -3328,7 +3328,7 @@
         <n v="3360000"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="Stage 2" numFmtId="165">
+    <cacheField name="Stage 2" numFmtId="164">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1300000" maxValue="9600000" count="6">
         <n v="1300000"/>
         <n v="1900000"/>
@@ -3338,10 +3338,10 @@
         <n v="6160000"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="Stage 3" numFmtId="165">
+    <cacheField name="Stage 3" numFmtId="164">
       <sharedItems containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="2300000" maxValue="15200000"/>
     </cacheField>
-    <cacheField name="Stage 4" numFmtId="165">
+    <cacheField name="Stage 4" numFmtId="164">
       <sharedItems containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="3900000" maxValue="32800000"/>
     </cacheField>
   </cacheFields>
@@ -3431,7 +3431,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{76FA9080-9907-4BEB-ACB7-E85178F5C4E7}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{76FA9080-9907-4BEB-ACB7-E85178F5C4E7}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="B14:F24" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField axis="axisRow" showAll="0">
@@ -3449,7 +3449,7 @@
       </items>
     </pivotField>
     <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="165" showAll="0">
+    <pivotField dataField="1" numFmtId="164" showAll="0">
       <items count="10">
         <item x="3"/>
         <item x="0"/>
@@ -3463,7 +3463,7 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField dataField="1" numFmtId="165" showAll="0">
+    <pivotField dataField="1" numFmtId="164" showAll="0">
       <items count="7">
         <item x="0"/>
         <item x="1"/>
@@ -4038,7 +4038,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4047,7 +4047,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1071EBF4-91EE-4334-B20E-AE85B91A2517}">
   <dimension ref="B1:G34"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="36" style="1" customWidth="1"/>
@@ -4059,36 +4059,36 @@
     <col min="8" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="30" customHeight="1"/>
-    <row r="2" spans="2:7" ht="25.5" customHeight="1">
+    <row r="1" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="5" t="s">
         <v>91</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="13"/>
-    </row>
-    <row r="3" spans="2:7" ht="25.5" customHeight="1">
+      <c r="G2" s="18"/>
+    </row>
+    <row r="3" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3">
         <v>840000</v>
       </c>
       <c r="D3" s="3">
         <v>1540000</v>
       </c>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-    </row>
-    <row r="4" spans="2:7" ht="6" customHeight="1">
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+    </row>
+    <row r="4" spans="2:7" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4"/>
       <c r="D4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="2:7">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>88</v>
       </c>
@@ -4102,7 +4102,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="6" spans="2:7">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
         <v>64</v>
       </c>
@@ -4116,7 +4116,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="7" spans="2:7">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>65</v>
       </c>
@@ -4130,7 +4130,7 @@
         <v>350000</v>
       </c>
     </row>
-    <row r="8" spans="2:7">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
         <v>4</v>
       </c>
@@ -4144,50 +4144,50 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="9" spans="2:7">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D9" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="2:7">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D10" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F10" s="10"/>
       <c r="G10" s="11"/>
     </row>
-    <row r="12" spans="2:7">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D12" s="10"/>
     </row>
-    <row r="14" spans="2:7" ht="26.25" customHeight="1">
+    <row r="14" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">
         <v>92</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="G14" s="13"/>
-    </row>
-    <row r="15" spans="2:7" ht="25.5" customHeight="1">
+      <c r="G14" s="18"/>
+    </row>
+    <row r="15" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="3">
         <v>2800000</v>
       </c>
       <c r="D15" s="3">
         <v>5400000</v>
       </c>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-    </row>
-    <row r="16" spans="2:7" ht="6.75" customHeight="1">
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+    </row>
+    <row r="16" spans="2:7" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="4"/>
       <c r="D16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
     </row>
-    <row r="17" spans="2:7">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
         <v>90</v>
       </c>
@@ -4201,7 +4201,7 @@
         <v>-50000</v>
       </c>
     </row>
-    <row r="18" spans="2:7">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
         <v>64</v>
       </c>
@@ -4216,7 +4216,7 @@
         <v>-50000 &amp; -25000</v>
       </c>
     </row>
-    <row r="19" spans="2:7">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="4" t="s">
         <v>57</v>
       </c>
@@ -4231,7 +4231,7 @@
         <v>-50% All Type</v>
       </c>
     </row>
-    <row r="20" spans="2:7">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="4" t="s">
         <v>48</v>
       </c>
@@ -4246,7 +4246,7 @@
         <v>-30% All Type</v>
       </c>
     </row>
-    <row r="21" spans="2:7">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
         <v>58</v>
       </c>
@@ -4254,7 +4254,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="2:7">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="4" t="s">
         <v>66</v>
       </c>
@@ -4262,7 +4262,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="23" spans="2:7">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="4" t="s">
         <v>4</v>
       </c>
@@ -4270,14 +4270,14 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="2:7">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D24" s="4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="25" spans="2:7" ht="15.75" customHeight="1"/>
-    <row r="26" spans="2:7" ht="15.75" customHeight="1"/>
-    <row r="34" spans="2:2">
+    <row r="25" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B34" s="12"/>
     </row>
   </sheetData>
@@ -4293,7 +4293,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ED714A2-7F80-46E3-BC42-5E655D5C93B7}">
   <dimension ref="B2:U42"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="13.140625" style="1" bestFit="1" customWidth="1"/>
@@ -4303,51 +4303,51 @@
     <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:21">
-      <c r="B2" s="15" t="s">
+    <row r="2" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B2" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="13" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="3" spans="2:21">
+    <row r="3" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
         <v>97</v>
       </c>
       <c r="C3" s="4">
         <v>4</v>
       </c>
-      <c r="D3" s="16">
+      <c r="D3" s="14">
         <f>C3*GRADUATION!B3</f>
         <v>860000</v>
       </c>
-      <c r="E3" s="16">
+      <c r="E3" s="14">
         <f>C3*GRADUATION!D3</f>
         <v>1300000</v>
       </c>
-      <c r="F3" s="16">
+      <c r="F3" s="14">
         <f>C3*GRADUATION!B14</f>
         <v>2300000</v>
       </c>
-      <c r="G3" s="16">
+      <c r="G3" s="14">
         <f>4*GRADUATION!D14</f>
         <v>3900000</v>
       </c>
     </row>
-    <row r="4" spans="2:21">
+    <row r="4" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>103</v>
       </c>
@@ -4355,23 +4355,23 @@
         <f>$C$3</f>
         <v>4</v>
       </c>
-      <c r="D4" s="16">
+      <c r="D4" s="14">
         <f>C4*COUPLE!B3</f>
         <v>940000</v>
       </c>
-      <c r="E4" s="16">
+      <c r="E4" s="14">
         <f>C4*COUPLE!D3</f>
         <v>1300000</v>
       </c>
-      <c r="F4" s="16">
+      <c r="F4" s="14">
         <f>C4*COUPLE!B14</f>
         <v>2460000</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="G4" s="14" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="5" spans="2:21">
+    <row r="5" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>104</v>
       </c>
@@ -4379,23 +4379,23 @@
         <f t="shared" ref="C5:C11" si="0">$C$3</f>
         <v>4</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="14">
         <f>C5*PERSONAL!B3</f>
         <v>900000</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="14">
         <f>C5*PERSONAL!D3</f>
         <v>1900000</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="14">
         <f>C5*PERSONAL!B14</f>
         <v>3660000</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="G5" s="14" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="6" spans="2:21">
+    <row r="6" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
         <v>105</v>
       </c>
@@ -4403,22 +4403,22 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="14">
         <f>C6*BEAUTY!B3</f>
         <v>700000</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="14">
         <f>BEAUTY!D3*C6</f>
         <v>1900000</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="G6" s="14" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="7" spans="2:21">
+    <row r="7" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>106</v>
       </c>
@@ -4426,24 +4426,24 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="14">
         <f>C7*PREWEDDING!B3</f>
         <v>1940000</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="14">
         <f>C7*PREWEDDING!D3</f>
         <v>3800000</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="14">
         <f>C7*PREWEDDING!B15</f>
         <v>7200000</v>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="14">
         <f>C7*PREWEDDING!D15</f>
         <v>15200000</v>
       </c>
     </row>
-    <row r="8" spans="2:21">
+    <row r="8" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
         <v>107</v>
       </c>
@@ -4451,24 +4451,24 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="14">
         <f>C8*WEDDING!B3</f>
         <v>5200000</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="14">
         <f>C8*WEDDING!D3</f>
         <v>9600000</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="14">
         <f>C8*WEDDING!B15</f>
         <v>15200000</v>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="14">
         <f>C8*WEDDING!D15</f>
         <v>32800000</v>
       </c>
     </row>
-    <row r="9" spans="2:21">
+    <row r="9" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>108</v>
       </c>
@@ -4476,24 +4476,24 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="14">
         <f>C9*ENGAGEMENT!B3</f>
         <v>2200000</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="14">
         <f>C9*ENGAGEMENT!D3</f>
         <v>3680000</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="14">
         <f>C9*ENGAGEMENT!B15</f>
         <v>6400000</v>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="14">
         <f>C9*ENGAGEMENT!D15</f>
         <v>19200000</v>
       </c>
     </row>
-    <row r="10" spans="2:21">
+    <row r="10" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
         <v>109</v>
       </c>
@@ -4501,24 +4501,24 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="14">
         <f>C10*EVENT!B3</f>
         <v>2080000</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="14">
         <f>C10*EVENT!D3</f>
         <v>3680000</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="14">
         <f>C10*EVENT!B15</f>
         <v>6400000</v>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="14">
         <f>C10*EVENT!D15</f>
         <v>19200000</v>
       </c>
     </row>
-    <row r="11" spans="2:21">
+    <row r="11" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>110</v>
       </c>
@@ -4526,25 +4526,25 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="14">
         <f>C11*TRAVEL!B3</f>
         <v>3360000</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="14">
         <f>C11*TRAVEL!D3</f>
         <v>6160000</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="14">
         <f>C11*TRAVEL!B15</f>
         <v>11200000</v>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="14">
         <f>C11*TRAVEL!D15</f>
         <v>21600000</v>
       </c>
     </row>
-    <row r="14" spans="2:21">
-      <c r="B14" s="17" t="s">
+    <row r="14" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B14" s="15" t="s">
         <v>113</v>
       </c>
       <c r="C14" t="s">
@@ -4575,20 +4575,20 @@
       <c r="T14"/>
       <c r="U14"/>
     </row>
-    <row r="15" spans="2:21">
-      <c r="B15" s="18" t="s">
+    <row r="15" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B15" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="C15" s="19">
+      <c r="C15" s="17">
         <v>700000</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="17">
         <v>1900000</v>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="17">
         <v>0</v>
       </c>
-      <c r="F15" s="19">
+      <c r="F15" s="17">
         <v>0</v>
       </c>
       <c r="G15"/>
@@ -4607,20 +4607,20 @@
       <c r="T15"/>
       <c r="U15"/>
     </row>
-    <row r="16" spans="2:21">
-      <c r="B16" s="18" t="s">
+    <row r="16" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B16" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C16" s="19">
+      <c r="C16" s="17">
         <v>940000</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="17">
         <v>1300000</v>
       </c>
-      <c r="E16" s="19">
+      <c r="E16" s="17">
         <v>2460000</v>
       </c>
-      <c r="F16" s="19">
+      <c r="F16" s="17">
         <v>0</v>
       </c>
       <c r="G16"/>
@@ -4639,20 +4639,20 @@
       <c r="T16"/>
       <c r="U16"/>
     </row>
-    <row r="17" spans="2:21">
-      <c r="B17" s="18" t="s">
+    <row r="17" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B17" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="C17" s="19">
+      <c r="C17" s="17">
         <v>2200000</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="17">
         <v>3680000</v>
       </c>
-      <c r="E17" s="19">
+      <c r="E17" s="17">
         <v>6400000</v>
       </c>
-      <c r="F17" s="19">
+      <c r="F17" s="17">
         <v>19200000</v>
       </c>
       <c r="G17"/>
@@ -4671,20 +4671,20 @@
       <c r="T17"/>
       <c r="U17"/>
     </row>
-    <row r="18" spans="2:21">
-      <c r="B18" s="18" t="s">
+    <row r="18" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B18" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="C18" s="19">
+      <c r="C18" s="17">
         <v>2080000</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="17">
         <v>3680000</v>
       </c>
-      <c r="E18" s="19">
+      <c r="E18" s="17">
         <v>6400000</v>
       </c>
-      <c r="F18" s="19">
+      <c r="F18" s="17">
         <v>19200000</v>
       </c>
       <c r="G18"/>
@@ -4703,20 +4703,20 @@
       <c r="T18"/>
       <c r="U18"/>
     </row>
-    <row r="19" spans="2:21">
-      <c r="B19" s="18" t="s">
+    <row r="19" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B19" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="C19" s="19">
+      <c r="C19" s="17">
         <v>860000</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="17">
         <v>1300000</v>
       </c>
-      <c r="E19" s="19">
+      <c r="E19" s="17">
         <v>2300000</v>
       </c>
-      <c r="F19" s="19">
+      <c r="F19" s="17">
         <v>3900000</v>
       </c>
       <c r="G19"/>
@@ -4735,20 +4735,20 @@
       <c r="T19"/>
       <c r="U19"/>
     </row>
-    <row r="20" spans="2:21">
-      <c r="B20" s="18" t="s">
+    <row r="20" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B20" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="C20" s="19">
+      <c r="C20" s="17">
         <v>900000</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="17">
         <v>1900000</v>
       </c>
-      <c r="E20" s="19">
+      <c r="E20" s="17">
         <v>3660000</v>
       </c>
-      <c r="F20" s="19">
+      <c r="F20" s="17">
         <v>0</v>
       </c>
       <c r="G20"/>
@@ -4767,20 +4767,20 @@
       <c r="T20"/>
       <c r="U20"/>
     </row>
-    <row r="21" spans="2:21">
-      <c r="B21" s="18" t="s">
+    <row r="21" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B21" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="C21" s="19">
+      <c r="C21" s="17">
         <v>1940000</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="17">
         <v>3800000</v>
       </c>
-      <c r="E21" s="19">
+      <c r="E21" s="17">
         <v>7200000</v>
       </c>
-      <c r="F21" s="19">
+      <c r="F21" s="17">
         <v>15200000</v>
       </c>
       <c r="G21"/>
@@ -4799,20 +4799,20 @@
       <c r="T21"/>
       <c r="U21"/>
     </row>
-    <row r="22" spans="2:21">
-      <c r="B22" s="18" t="s">
+    <row r="22" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B22" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="C22" s="19">
+      <c r="C22" s="17">
         <v>3360000</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="17">
         <v>6160000</v>
       </c>
-      <c r="E22" s="19">
+      <c r="E22" s="17">
         <v>11200000</v>
       </c>
-      <c r="F22" s="19">
+      <c r="F22" s="17">
         <v>21600000</v>
       </c>
       <c r="G22"/>
@@ -4831,20 +4831,20 @@
       <c r="T22"/>
       <c r="U22"/>
     </row>
-    <row r="23" spans="2:21">
-      <c r="B23" s="18" t="s">
+    <row r="23" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B23" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="C23" s="19">
+      <c r="C23" s="17">
         <v>5200000</v>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="17">
         <v>9600000</v>
       </c>
-      <c r="E23" s="19">
+      <c r="E23" s="17">
         <v>15200000</v>
       </c>
-      <c r="F23" s="19">
+      <c r="F23" s="17">
         <v>32800000</v>
       </c>
       <c r="G23"/>
@@ -4863,20 +4863,20 @@
       <c r="T23"/>
       <c r="U23"/>
     </row>
-    <row r="24" spans="2:21">
-      <c r="B24" s="18" t="s">
+    <row r="24" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B24" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="C24" s="19">
+      <c r="C24" s="17">
         <v>18180000</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="17">
         <v>33320000</v>
       </c>
-      <c r="E24" s="19">
+      <c r="E24" s="17">
         <v>54820000</v>
       </c>
-      <c r="F24" s="19">
+      <c r="F24" s="17">
         <v>111900000</v>
       </c>
       <c r="G24"/>
@@ -4895,7 +4895,7 @@
       <c r="T24"/>
       <c r="U24"/>
     </row>
-    <row r="25" spans="2:21">
+    <row r="25" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B25"/>
       <c r="C25"/>
       <c r="D25"/>
@@ -4917,7 +4917,7 @@
       <c r="T25"/>
       <c r="U25"/>
     </row>
-    <row r="26" spans="2:21">
+    <row r="26" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B26"/>
       <c r="C26"/>
       <c r="D26"/>
@@ -4939,7 +4939,7 @@
       <c r="T26"/>
       <c r="U26"/>
     </row>
-    <row r="27" spans="2:21">
+    <row r="27" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B27"/>
       <c r="C27"/>
       <c r="D27"/>
@@ -4952,7 +4952,7 @@
       <c r="K27"/>
       <c r="L27"/>
     </row>
-    <row r="28" spans="2:21">
+    <row r="28" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B28"/>
       <c r="C28"/>
       <c r="D28"/>
@@ -4965,7 +4965,7 @@
       <c r="K28"/>
       <c r="L28"/>
     </row>
-    <row r="29" spans="2:21">
+    <row r="29" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B29"/>
       <c r="C29"/>
       <c r="D29"/>
@@ -4978,7 +4978,7 @@
       <c r="K29"/>
       <c r="L29"/>
     </row>
-    <row r="30" spans="2:21">
+    <row r="30" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B30"/>
       <c r="C30"/>
       <c r="D30"/>
@@ -4991,7 +4991,7 @@
       <c r="K30"/>
       <c r="L30"/>
     </row>
-    <row r="31" spans="2:21">
+    <row r="31" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B31"/>
       <c r="C31"/>
       <c r="D31"/>
@@ -5004,7 +5004,7 @@
       <c r="K31"/>
       <c r="L31"/>
     </row>
-    <row r="32" spans="2:21">
+    <row r="32" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B32"/>
       <c r="C32"/>
       <c r="D32"/>
@@ -5017,7 +5017,7 @@
       <c r="K32"/>
       <c r="L32"/>
     </row>
-    <row r="33" spans="2:12">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B33"/>
       <c r="C33"/>
       <c r="D33"/>
@@ -5030,7 +5030,7 @@
       <c r="K33"/>
       <c r="L33"/>
     </row>
-    <row r="34" spans="2:12">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B34"/>
       <c r="C34"/>
       <c r="D34"/>
@@ -5043,28 +5043,28 @@
       <c r="K34"/>
       <c r="L34"/>
     </row>
-    <row r="35" spans="2:12">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B35"/>
     </row>
-    <row r="36" spans="2:12">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B36"/>
     </row>
-    <row r="37" spans="2:12">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B37"/>
     </row>
-    <row r="38" spans="2:12">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B38"/>
     </row>
-    <row r="39" spans="2:12">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B39"/>
     </row>
-    <row r="40" spans="2:12">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B40"/>
     </row>
-    <row r="41" spans="2:12">
+    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B41"/>
     </row>
-    <row r="42" spans="2:12">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B42"/>
     </row>
   </sheetData>
@@ -5074,9 +5074,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BA0498E-CFF0-4389-A69A-34CB8E5E601C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F09C4C1-1C9C-429F-AA75-8EBC75D29B6C}">
   <dimension ref="B1:G25"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="36" style="1" customWidth="1"/>
@@ -5088,41 +5088,41 @@
     <col min="8" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="30" customHeight="1"/>
-    <row r="2" spans="2:7" ht="25.5" customHeight="1">
+    <row r="1" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="13"/>
-    </row>
-    <row r="3" spans="2:7" ht="25.5" customHeight="1">
+      <c r="G2" s="18"/>
+    </row>
+    <row r="3" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3">
-        <v>215000</v>
+        <v>225000</v>
       </c>
       <c r="D3" s="3">
-        <v>325000</v>
-      </c>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-    </row>
-    <row r="4" spans="2:7" ht="6" customHeight="1">
+        <v>475000</v>
+      </c>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+    </row>
+    <row r="4" spans="2:7" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4"/>
       <c r="D4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="2:7">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>17</v>
@@ -5131,12 +5131,12 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="6" spans="2:7">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>1</v>
@@ -5145,7 +5145,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="7" spans="2:7">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>3</v>
       </c>
@@ -5159,7 +5159,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="8" spans="2:7">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
         <v>4</v>
       </c>
@@ -5173,7 +5173,7 @@
         <v>35000</v>
       </c>
     </row>
-    <row r="9" spans="2:7">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D9" s="4" t="s">
         <v>7</v>
       </c>
@@ -5184,41 +5184,40 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="26.25" customHeight="1">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="D10" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="8"/>
+      <c r="F13" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="G13" s="13"/>
-    </row>
-    <row r="14" spans="2:7" ht="25.5" customHeight="1">
+      <c r="G13" s="18"/>
+    </row>
+    <row r="14" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="3">
-        <v>575000</v>
-      </c>
-      <c r="D14" s="3">
-        <v>975000</v>
-      </c>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-    </row>
-    <row r="15" spans="2:7" ht="6.75" customHeight="1">
+        <v>915000</v>
+      </c>
+      <c r="D14" s="9"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+    </row>
+    <row r="15" spans="2:7" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="4"/>
-      <c r="D15" s="4"/>
+      <c r="D15" s="10"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
     </row>
-    <row r="16" spans="2:7">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>14</v>
-      </c>
+      <c r="D16" s="10"/>
       <c r="F16" s="4" t="s">
         <v>20</v>
       </c>
@@ -5226,13 +5225,11 @@
         <v>-50000</v>
       </c>
     </row>
-    <row r="17" spans="2:7">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>13</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="D17" s="10"/>
       <c r="F17" s="4" t="s">
         <v>21</v>
       </c>
@@ -5241,13 +5238,11 @@
         <v>-50000 &amp; -25000</v>
       </c>
     </row>
-    <row r="18" spans="2:7">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="D18" s="10"/>
       <c r="F18" s="4" t="s">
         <v>22</v>
       </c>
@@ -5256,31 +5251,30 @@
         <v>-50% All Type</v>
       </c>
     </row>
-    <row r="19" spans="2:7">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7">
+      <c r="D19" s="10"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7">
+      <c r="D20" s="10"/>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" ht="26.25" customHeight="1"/>
+        <v>33</v>
+      </c>
+      <c r="D21" s="10"/>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="F2:G3"/>
@@ -5292,9 +5286,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4510C927-4F2F-4896-BBDB-E8861F8EED92}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3624BA3E-0F1D-4DE8-8401-F1BA58FC44F6}">
   <dimension ref="B1:G25"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="36" style="1" customWidth="1"/>
@@ -5306,41 +5300,41 @@
     <col min="8" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="30" customHeight="1"/>
-    <row r="2" spans="2:7" ht="25.5" customHeight="1">
+    <row r="1" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="13"/>
-    </row>
-    <row r="3" spans="2:7" ht="25.5" customHeight="1">
+      <c r="G2" s="18"/>
+    </row>
+    <row r="3" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3">
-        <v>235000</v>
+        <v>175000</v>
       </c>
       <c r="D3" s="3">
-        <v>325000</v>
-      </c>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-    </row>
-    <row r="4" spans="2:7" ht="6" customHeight="1">
+        <v>475000</v>
+      </c>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+    </row>
+    <row r="4" spans="2:7" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4"/>
       <c r="D4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="2:7">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>17</v>
@@ -5349,12 +5343,12 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="6" spans="2:7">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>1</v>
@@ -5363,12 +5357,12 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="7" spans="2:7">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>18</v>
@@ -5377,12 +5371,12 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="8" spans="2:7">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>3</v>
@@ -5391,9 +5385,9 @@
         <v>35000</v>
       </c>
     </row>
-    <row r="9" spans="2:7">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D9" s="4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>19</v>
@@ -5402,34 +5396,38 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="26.25" customHeight="1">
-      <c r="B13" s="2" t="s">
-        <v>27</v>
-      </c>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="D10" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="D11" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="8"/>
       <c r="D13" s="8"/>
-      <c r="F13" s="14" t="s">
+      <c r="F13" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="G13" s="13"/>
-    </row>
-    <row r="14" spans="2:7" ht="25.5" customHeight="1">
-      <c r="B14" s="3">
-        <v>615000</v>
-      </c>
+      <c r="G13" s="18"/>
+    </row>
+    <row r="14" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="9"/>
       <c r="D14" s="9"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-    </row>
-    <row r="15" spans="2:7" ht="6.75" customHeight="1">
-      <c r="B15" s="4"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+    </row>
+    <row r="15" spans="2:7" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="10"/>
       <c r="D15" s="10"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
     </row>
-    <row r="16" spans="2:7">
-      <c r="B16" s="4" t="s">
-        <v>9</v>
-      </c>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="10"/>
       <c r="D16" s="10"/>
       <c r="F16" s="4" t="s">
         <v>20</v>
@@ -5438,10 +5436,8 @@
         <v>-50000</v>
       </c>
     </row>
-    <row r="17" spans="2:7">
-      <c r="B17" s="4" t="s">
-        <v>28</v>
-      </c>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="10"/>
       <c r="D17" s="10"/>
       <c r="F17" s="4" t="s">
         <v>21</v>
@@ -5451,10 +5447,8 @@
         <v>-50000 &amp; -25000</v>
       </c>
     </row>
-    <row r="18" spans="2:7">
-      <c r="B18" s="4" t="s">
-        <v>11</v>
-      </c>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="10"/>
       <c r="D18" s="10"/>
       <c r="F18" s="4" t="s">
         <v>22</v>
@@ -5464,30 +5458,22 @@
         <v>-50% All Type</v>
       </c>
     </row>
-    <row r="19" spans="2:7">
-      <c r="B19" s="4" t="s">
-        <v>4</v>
-      </c>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="10"/>
       <c r="D19" s="10"/>
     </row>
-    <row r="20" spans="2:7">
-      <c r="B20" s="4" t="s">
-        <v>7</v>
-      </c>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="10"/>
       <c r="D20" s="10"/>
     </row>
-    <row r="21" spans="2:7">
-      <c r="B21" s="4" t="s">
-        <v>12</v>
-      </c>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="10"/>
       <c r="D21" s="10"/>
     </row>
-    <row r="22" spans="2:7">
-      <c r="B22" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" ht="26.25" customHeight="1"/>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="10"/>
+    </row>
+    <row r="25" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="F2:G3"/>
@@ -5499,9 +5485,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F09C4C1-1C9C-429F-AA75-8EBC75D29B6C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BA0498E-CFF0-4389-A69A-34CB8E5E601C}">
   <dimension ref="B1:G25"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="36" style="1" customWidth="1"/>
@@ -5513,41 +5499,41 @@
     <col min="8" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="30" customHeight="1"/>
-    <row r="2" spans="2:7" ht="25.5" customHeight="1">
+    <row r="1" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F2" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="13"/>
-    </row>
-    <row r="3" spans="2:7" ht="25.5" customHeight="1">
+      <c r="G2" s="18"/>
+    </row>
+    <row r="3" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3">
-        <v>225000</v>
+        <v>215000</v>
       </c>
       <c r="D3" s="3">
-        <v>475000</v>
-      </c>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-    </row>
-    <row r="4" spans="2:7" ht="6" customHeight="1">
+        <v>325000</v>
+      </c>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+    </row>
+    <row r="4" spans="2:7" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4"/>
       <c r="D4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="2:7">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>17</v>
@@ -5556,12 +5542,12 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="6" spans="2:7">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>1</v>
@@ -5570,7 +5556,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="7" spans="2:7">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>3</v>
       </c>
@@ -5584,7 +5570,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="8" spans="2:7">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
         <v>4</v>
       </c>
@@ -5598,7 +5584,7 @@
         <v>35000</v>
       </c>
     </row>
-    <row r="9" spans="2:7">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D9" s="4" t="s">
         <v>7</v>
       </c>
@@ -5609,40 +5595,41 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="10" spans="2:7">
-      <c r="D10" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" ht="26.25" customHeight="1">
+    <row r="13" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" s="8"/>
-      <c r="F13" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="G13" s="13"/>
-    </row>
-    <row r="14" spans="2:7" ht="25.5" customHeight="1">
+      <c r="G13" s="18"/>
+    </row>
+    <row r="14" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="3">
-        <v>915000</v>
-      </c>
-      <c r="D14" s="9"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-    </row>
-    <row r="15" spans="2:7" ht="6.75" customHeight="1">
+        <v>575000</v>
+      </c>
+      <c r="D14" s="3">
+        <v>975000</v>
+      </c>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+    </row>
+    <row r="15" spans="2:7" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="4"/>
-      <c r="D15" s="10"/>
+      <c r="D15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
     </row>
-    <row r="16" spans="2:7">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="10"/>
+      <c r="D16" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="F16" s="4" t="s">
         <v>20</v>
       </c>
@@ -5650,11 +5637,13 @@
         <v>-50000</v>
       </c>
     </row>
-    <row r="17" spans="2:7">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" s="10"/>
+        <v>10</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F17" s="4" t="s">
         <v>21</v>
       </c>
@@ -5663,11 +5652,13 @@
         <v>-50000 &amp; -25000</v>
       </c>
     </row>
-    <row r="18" spans="2:7">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="10"/>
+      <c r="D18" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="F18" s="4" t="s">
         <v>22</v>
       </c>
@@ -5676,30 +5667,31 @@
         <v>-50% All Type</v>
       </c>
     </row>
-    <row r="19" spans="2:7">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D19" s="10"/>
-    </row>
-    <row r="20" spans="2:7">
+      <c r="D19" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="10"/>
-    </row>
-    <row r="21" spans="2:7">
+      <c r="D20" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D21" s="10"/>
-    </row>
-    <row r="22" spans="2:7">
-      <c r="B22" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" ht="26.25" customHeight="1"/>
+        <v>12</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="F2:G3"/>
@@ -5711,9 +5703,9 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3624BA3E-0F1D-4DE8-8401-F1BA58FC44F6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4510C927-4F2F-4896-BBDB-E8861F8EED92}">
   <dimension ref="B1:G25"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="36" style="1" customWidth="1"/>
@@ -5725,41 +5717,41 @@
     <col min="8" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="30" customHeight="1"/>
-    <row r="2" spans="2:7" ht="25.5" customHeight="1">
+    <row r="1" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F2" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="13"/>
-    </row>
-    <row r="3" spans="2:7" ht="25.5" customHeight="1">
+      <c r="G2" s="18"/>
+    </row>
+    <row r="3" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3">
-        <v>175000</v>
+        <v>235000</v>
       </c>
       <c r="D3" s="3">
-        <v>475000</v>
-      </c>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-    </row>
-    <row r="4" spans="2:7" ht="6" customHeight="1">
+        <v>325000</v>
+      </c>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+    </row>
+    <row r="4" spans="2:7" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4"/>
       <c r="D4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="2:7">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>17</v>
@@ -5768,12 +5760,12 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="6" spans="2:7">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>1</v>
@@ -5782,12 +5774,12 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="7" spans="2:7">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>18</v>
@@ -5796,12 +5788,12 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="8" spans="2:7">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>3</v>
@@ -5810,9 +5802,9 @@
         <v>35000</v>
       </c>
     </row>
-    <row r="9" spans="2:7">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D9" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>19</v>
@@ -5821,38 +5813,34 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="10" spans="2:7">
-      <c r="D10" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7">
-      <c r="D11" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" ht="26.25" customHeight="1">
-      <c r="B13" s="8"/>
+    <row r="13" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="D13" s="8"/>
-      <c r="F13" s="14" t="s">
+      <c r="F13" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="G13" s="13"/>
-    </row>
-    <row r="14" spans="2:7" ht="25.5" customHeight="1">
-      <c r="B14" s="9"/>
+      <c r="G13" s="18"/>
+    </row>
+    <row r="14" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="3">
+        <v>615000</v>
+      </c>
       <c r="D14" s="9"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-    </row>
-    <row r="15" spans="2:7" ht="6.75" customHeight="1">
-      <c r="B15" s="10"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+    </row>
+    <row r="15" spans="2:7" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="4"/>
       <c r="D15" s="10"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
     </row>
-    <row r="16" spans="2:7">
-      <c r="B16" s="10"/>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="4" t="s">
+        <v>9</v>
+      </c>
       <c r="D16" s="10"/>
       <c r="F16" s="4" t="s">
         <v>20</v>
@@ -5861,8 +5849,10 @@
         <v>-50000</v>
       </c>
     </row>
-    <row r="17" spans="2:7">
-      <c r="B17" s="10"/>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="4" t="s">
+        <v>28</v>
+      </c>
       <c r="D17" s="10"/>
       <c r="F17" s="4" t="s">
         <v>21</v>
@@ -5872,8 +5862,10 @@
         <v>-50000 &amp; -25000</v>
       </c>
     </row>
-    <row r="18" spans="2:7">
-      <c r="B18" s="10"/>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="D18" s="10"/>
       <c r="F18" s="4" t="s">
         <v>22</v>
@@ -5883,22 +5875,30 @@
         <v>-50% All Type</v>
       </c>
     </row>
-    <row r="19" spans="2:7">
-      <c r="B19" s="10"/>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="D19" s="10"/>
     </row>
-    <row r="20" spans="2:7">
-      <c r="B20" s="10"/>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="D20" s="10"/>
     </row>
-    <row r="21" spans="2:7">
-      <c r="B21" s="10"/>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="D21" s="10"/>
     </row>
-    <row r="22" spans="2:7">
-      <c r="B22" s="10"/>
-    </row>
-    <row r="25" spans="2:7" ht="26.25" customHeight="1"/>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="F2:G3"/>
@@ -5912,7 +5912,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFE228C7-FCFA-41CE-86C8-CD4AD79C92B0}">
   <dimension ref="B1:G29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="36" style="1" customWidth="1"/>
@@ -5924,36 +5924,36 @@
     <col min="8" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="30" customHeight="1"/>
-    <row r="2" spans="2:7" ht="25.5" customHeight="1">
+    <row r="1" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="13"/>
-    </row>
-    <row r="3" spans="2:7" ht="25.5" customHeight="1">
+      <c r="G2" s="18"/>
+    </row>
+    <row r="3" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3">
         <v>485000</v>
       </c>
       <c r="D3" s="3">
         <v>950000</v>
       </c>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-    </row>
-    <row r="4" spans="2:7" ht="6" customHeight="1">
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+    </row>
+    <row r="4" spans="2:7" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4"/>
       <c r="D4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="2:7">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
@@ -5967,7 +5967,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="6" spans="2:7">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
         <v>40</v>
       </c>
@@ -5981,7 +5981,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="7" spans="2:7">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>41</v>
       </c>
@@ -5995,7 +5995,7 @@
         <v>350000</v>
       </c>
     </row>
-    <row r="8" spans="2:7">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
         <v>3</v>
       </c>
@@ -6009,7 +6009,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="9" spans="2:7">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>4</v>
       </c>
@@ -6017,50 +6017,50 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:7">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D10" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F10" s="10"/>
       <c r="G10" s="11"/>
     </row>
-    <row r="11" spans="2:7">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D11" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="2:7">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D12" s="10"/>
     </row>
-    <row r="14" spans="2:7" ht="26.25" customHeight="1">
+    <row r="14" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>44</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="G14" s="13"/>
-    </row>
-    <row r="15" spans="2:7" ht="25.5" customHeight="1">
+      <c r="G14" s="18"/>
+    </row>
+    <row r="15" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="3">
         <v>1800000</v>
       </c>
       <c r="D15" s="3">
         <v>3800000</v>
       </c>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-    </row>
-    <row r="16" spans="2:7" ht="6.75" customHeight="1">
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+    </row>
+    <row r="16" spans="2:7" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="4"/>
       <c r="D16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
     </row>
-    <row r="17" spans="2:7">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
         <v>45</v>
       </c>
@@ -6074,7 +6074,7 @@
         <v>-50000</v>
       </c>
     </row>
-    <row r="18" spans="2:7">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
         <v>40</v>
       </c>
@@ -6089,7 +6089,7 @@
         <v>-50000 &amp; -25000</v>
       </c>
     </row>
-    <row r="19" spans="2:7">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="4" t="s">
         <v>46</v>
       </c>
@@ -6104,7 +6104,7 @@
         <v>-50% All Type</v>
       </c>
     </row>
-    <row r="20" spans="2:7">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="4" t="s">
         <v>38</v>
       </c>
@@ -6112,7 +6112,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="2:7">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
         <v>47</v>
       </c>
@@ -6120,7 +6120,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="2:7">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="4" t="s">
         <v>4</v>
       </c>
@@ -6128,7 +6128,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="2:7">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="4" t="s">
         <v>7</v>
       </c>
@@ -6136,7 +6136,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="24" spans="2:7">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="4" t="s">
         <v>48</v>
       </c>
@@ -6144,7 +6144,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="2:7" ht="15.75" customHeight="1">
+    <row r="25" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="4" t="s">
         <v>49</v>
       </c>
@@ -6152,22 +6152,22 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="2:7" ht="15.75" customHeight="1">
+    <row r="26" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="27" spans="2:7">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D27" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="28" spans="2:7">
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D28" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="2:7">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D29" s="4" t="s">
         <v>59</v>
       </c>
@@ -6185,7 +6185,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C7E75C3-91B2-44EA-9723-79A38490D984}">
   <dimension ref="B1:G28"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="36" style="1" customWidth="1"/>
@@ -6197,36 +6197,36 @@
     <col min="8" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="30" customHeight="1"/>
-    <row r="2" spans="2:7" ht="25.5" customHeight="1">
+    <row r="1" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="13"/>
-    </row>
-    <row r="3" spans="2:7" ht="25.5" customHeight="1">
+      <c r="G2" s="18"/>
+    </row>
+    <row r="3" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3">
         <v>1300000</v>
       </c>
       <c r="D3" s="3">
         <v>2400000</v>
       </c>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-    </row>
-    <row r="4" spans="2:7" ht="6" customHeight="1">
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+    </row>
+    <row r="4" spans="2:7" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4"/>
       <c r="D4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="2:7">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>63</v>
       </c>
@@ -6240,7 +6240,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="6" spans="2:7">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
         <v>64</v>
       </c>
@@ -6254,7 +6254,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="7" spans="2:7">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>48</v>
       </c>
@@ -6268,7 +6268,7 @@
         <v>350000</v>
       </c>
     </row>
-    <row r="8" spans="2:7">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
         <v>65</v>
       </c>
@@ -6282,7 +6282,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="9" spans="2:7">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>4</v>
       </c>
@@ -6290,45 +6290,45 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="2:7">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D10" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F10" s="10"/>
       <c r="G10" s="11"/>
     </row>
-    <row r="12" spans="2:7">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D12" s="10"/>
     </row>
-    <row r="14" spans="2:7" ht="26.25" customHeight="1">
+    <row r="14" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="G14" s="13"/>
-    </row>
-    <row r="15" spans="2:7" ht="25.5" customHeight="1">
+      <c r="G14" s="18"/>
+    </row>
+    <row r="15" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="3">
         <v>3800000</v>
       </c>
       <c r="D15" s="3">
         <v>8200000</v>
       </c>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-    </row>
-    <row r="16" spans="2:7" ht="6.75" customHeight="1">
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+    </row>
+    <row r="16" spans="2:7" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="4"/>
       <c r="D16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
     </row>
-    <row r="17" spans="2:7">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
         <v>70</v>
       </c>
@@ -6342,7 +6342,7 @@
         <v>-50000</v>
       </c>
     </row>
-    <row r="18" spans="2:7">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
         <v>64</v>
       </c>
@@ -6357,7 +6357,7 @@
         <v>-50000 &amp; -25000</v>
       </c>
     </row>
-    <row r="19" spans="2:7">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="4" t="s">
         <v>57</v>
       </c>
@@ -6372,7 +6372,7 @@
         <v>-50% All Type</v>
       </c>
     </row>
-    <row r="20" spans="2:7">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="4" t="s">
         <v>69</v>
       </c>
@@ -6380,7 +6380,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="2:7">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
         <v>58</v>
       </c>
@@ -6388,7 +6388,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="2:7">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="4" t="s">
         <v>66</v>
       </c>
@@ -6396,7 +6396,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="23" spans="2:7">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="4" t="s">
         <v>4</v>
       </c>
@@ -6404,27 +6404,27 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="2:7">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D24" s="4" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="2:7" ht="15.75" customHeight="1">
+    <row r="25" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D25" s="4" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="26" spans="2:7" ht="15.75" customHeight="1">
+    <row r="26" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="4" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="27" spans="2:7">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D27" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="28" spans="2:7">
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D28" s="4" t="s">
         <v>59</v>
       </c>
@@ -6442,7 +6442,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{757F7258-105E-4A19-B86D-E5B2236F720D}">
   <dimension ref="B1:G34"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="36" style="1" customWidth="1"/>
@@ -6454,36 +6454,36 @@
     <col min="8" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="30" customHeight="1"/>
-    <row r="2" spans="2:7" ht="25.5" customHeight="1">
+    <row r="1" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>84</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="13"/>
-    </row>
-    <row r="3" spans="2:7" ht="25.5" customHeight="1">
+      <c r="G2" s="18"/>
+    </row>
+    <row r="3" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3">
         <v>550000</v>
       </c>
       <c r="D3" s="3">
         <v>920000</v>
       </c>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-    </row>
-    <row r="4" spans="2:7" ht="6" customHeight="1">
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+    </row>
+    <row r="4" spans="2:7" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4"/>
       <c r="D4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="2:7">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>80</v>
       </c>
@@ -6497,7 +6497,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="6" spans="2:7">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
         <v>64</v>
       </c>
@@ -6511,7 +6511,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="7" spans="2:7">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>48</v>
       </c>
@@ -6525,7 +6525,7 @@
         <v>350000</v>
       </c>
     </row>
-    <row r="8" spans="2:7">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
         <v>65</v>
       </c>
@@ -6539,7 +6539,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="9" spans="2:7">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>4</v>
       </c>
@@ -6547,45 +6547,45 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="2:7">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D10" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F10" s="10"/>
       <c r="G10" s="11"/>
     </row>
-    <row r="12" spans="2:7">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D12" s="10"/>
     </row>
-    <row r="14" spans="2:7" ht="26.25" customHeight="1">
+    <row r="14" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>78</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="G14" s="13"/>
-    </row>
-    <row r="15" spans="2:7" ht="25.5" customHeight="1">
+      <c r="G14" s="18"/>
+    </row>
+    <row r="15" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="3">
         <v>1600000</v>
       </c>
       <c r="D15" s="3">
         <v>4800000</v>
       </c>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-    </row>
-    <row r="16" spans="2:7" ht="6.75" customHeight="1">
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+    </row>
+    <row r="16" spans="2:7" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="4"/>
       <c r="D16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
     </row>
-    <row r="17" spans="2:7">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
         <v>81</v>
       </c>
@@ -6599,7 +6599,7 @@
         <v>-50000</v>
       </c>
     </row>
-    <row r="18" spans="2:7">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
         <v>64</v>
       </c>
@@ -6614,7 +6614,7 @@
         <v>-50000 &amp; -25000</v>
       </c>
     </row>
-    <row r="19" spans="2:7">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="4" t="s">
         <v>57</v>
       </c>
@@ -6629,7 +6629,7 @@
         <v>-50% All Type</v>
       </c>
     </row>
-    <row r="20" spans="2:7">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="4" t="s">
         <v>69</v>
       </c>
@@ -6637,7 +6637,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="2:7">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
         <v>58</v>
       </c>
@@ -6645,7 +6645,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="2:7">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="4" t="s">
         <v>66</v>
       </c>
@@ -6653,7 +6653,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="23" spans="2:7">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="4" t="s">
         <v>4</v>
       </c>
@@ -6661,27 +6661,27 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="2:7">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D24" s="4" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="2:7" ht="15.75" customHeight="1">
+    <row r="25" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D25" s="4" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="26" spans="2:7" ht="15.75" customHeight="1">
+    <row r="26" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="27" spans="2:7">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D27" s="4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="34" spans="2:2">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B34" s="12"/>
     </row>
   </sheetData>
@@ -6697,7 +6697,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{124CE633-E2C2-45EB-9187-AAB4045A946D}">
   <dimension ref="B1:G34"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="36" style="1" customWidth="1"/>
@@ -6709,36 +6709,36 @@
     <col min="8" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="30" customHeight="1"/>
-    <row r="2" spans="2:7" ht="25.5" customHeight="1">
+    <row r="1" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="5" t="s">
         <v>85</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="13"/>
-    </row>
-    <row r="3" spans="2:7" ht="25.5" customHeight="1">
+      <c r="G2" s="18"/>
+    </row>
+    <row r="3" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3">
         <v>520000</v>
       </c>
       <c r="D3" s="3">
         <v>920000</v>
       </c>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-    </row>
-    <row r="4" spans="2:7" ht="6" customHeight="1">
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+    </row>
+    <row r="4" spans="2:7" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4"/>
       <c r="D4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="2:7">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>80</v>
       </c>
@@ -6752,7 +6752,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="6" spans="2:7">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
         <v>64</v>
       </c>
@@ -6766,7 +6766,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="7" spans="2:7">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>65</v>
       </c>
@@ -6780,7 +6780,7 @@
         <v>350000</v>
       </c>
     </row>
-    <row r="8" spans="2:7">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
         <v>4</v>
       </c>
@@ -6794,50 +6794,50 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="9" spans="2:7">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D9" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="2:7">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D10" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F10" s="10"/>
       <c r="G10" s="11"/>
     </row>
-    <row r="12" spans="2:7">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D12" s="10"/>
     </row>
-    <row r="14" spans="2:7" ht="26.25" customHeight="1">
+    <row r="14" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">
         <v>86</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="G14" s="13"/>
-    </row>
-    <row r="15" spans="2:7" ht="25.5" customHeight="1">
+      <c r="G14" s="18"/>
+    </row>
+    <row r="15" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="3">
         <v>1600000</v>
       </c>
       <c r="D15" s="3">
         <v>4800000</v>
       </c>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-    </row>
-    <row r="16" spans="2:7" ht="6.75" customHeight="1">
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+    </row>
+    <row r="16" spans="2:7" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="4"/>
       <c r="D16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
     </row>
-    <row r="17" spans="2:7">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
         <v>81</v>
       </c>
@@ -6851,7 +6851,7 @@
         <v>-50000</v>
       </c>
     </row>
-    <row r="18" spans="2:7">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
         <v>64</v>
       </c>
@@ -6866,7 +6866,7 @@
         <v>-50000 &amp; -25000</v>
       </c>
     </row>
-    <row r="19" spans="2:7">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="4" t="s">
         <v>57</v>
       </c>
@@ -6881,7 +6881,7 @@
         <v>-50% All Type</v>
       </c>
     </row>
-    <row r="20" spans="2:7">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="4" t="s">
         <v>69</v>
       </c>
@@ -6889,7 +6889,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="2:7">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
         <v>58</v>
       </c>
@@ -6897,7 +6897,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="2:7">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="4" t="s">
         <v>66</v>
       </c>
@@ -6905,7 +6905,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="23" spans="2:7">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="4" t="s">
         <v>4</v>
       </c>
@@ -6913,14 +6913,14 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="2:7">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D24" s="4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="25" spans="2:7" ht="15.75" customHeight="1"/>
-    <row r="26" spans="2:7" ht="15.75" customHeight="1"/>
-    <row r="34" spans="2:2">
+    <row r="25" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B34" s="12"/>
     </row>
   </sheetData>
